--- a/artfynd/Sjättnäsbäcken SCA artfynd.xlsx
+++ b/artfynd/Sjättnäsbäcken SCA artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110787321</v>
+        <v>16847436</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högberget, Nederhögen, Jmt</t>
+          <t>Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470918</v>
+        <v>471241</v>
       </c>
       <c r="R2" t="n">
-        <v>6922468</v>
+        <v>6922501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2014-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2014-06-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,62 +757,61 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Niina Sallmén, sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110787320</v>
+        <v>110787318</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470919</v>
+        <v>470953</v>
       </c>
       <c r="R3" t="n">
-        <v>6922469</v>
+        <v>6922579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,17 +870,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16847436</v>
+        <v>110787319</v>
       </c>
       <c r="B4" t="n">
-        <v>80433</v>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högberget, Jmt</t>
+          <t>Högberget, Nederhögen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471241</v>
+        <v>470915</v>
       </c>
       <c r="R4" t="n">
-        <v>6922501</v>
+        <v>6922506</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-06-10</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-06-10</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,61 +980,62 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrskog</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110787318</v>
+        <v>110787316</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470953</v>
+        <v>470762</v>
       </c>
       <c r="R5" t="n">
-        <v>6922579</v>
+        <v>6922583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110787319</v>
+        <v>110787321</v>
       </c>
       <c r="B6" t="n">
-        <v>83307</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470915</v>
+        <v>470918</v>
       </c>
       <c r="R6" t="n">
-        <v>6922506</v>
+        <v>6922468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110787316</v>
+        <v>110787320</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470762</v>
+        <v>470919</v>
       </c>
       <c r="R7" t="n">
-        <v>6922583</v>
+        <v>6922469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
